--- a/BOM/Task4/BOM.xlsx
+++ b/BOM/Task4/BOM.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="BOM Sheet" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="8+2 Sensor Impact Analysis" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,9 +12,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="135">
+  <si>
+    <t>Component</t>
+  </si>
   <si>
     <t>Bill of Materials (BOM)</t>
+  </si>
+  <si>
+    <t>Current Setup</t>
+  </si>
+  <si>
+    <t>Proposed 8+2 Setup</t>
+  </si>
+  <si>
+    <t>Impact / Notes</t>
+  </si>
+  <si>
+    <t>IR Array</t>
+  </si>
+  <si>
+    <t>5-Channel TCRT5000</t>
+  </si>
+  <si>
+    <t>8-Channel Array + 2 Wing Sensors</t>
+  </si>
+  <si>
+    <t>Requires sourcing new sensor arrays or custom PCB. Cost will increase.</t>
+  </si>
+  <si>
+    <t>Microcontroller</t>
+  </si>
+  <si>
+    <t>ESP32-WROOM-32 (30-pin)</t>
+  </si>
+  <si>
+    <t>ESP32-WROOM-32 (30-pin) or upgrade</t>
+  </si>
+  <si>
+    <t>Needs 10 GPIOs for sensors. May require upgrading to 38-pin ESP32 if pins are exhausted by encoders/motors.</t>
+  </si>
+  <si>
+    <t>Jumper Wires</t>
+  </si>
+  <si>
+    <t>10CM F-F &amp; M-F (40 Pcs each)</t>
+  </si>
+  <si>
+    <t>More wires needed (10 signal + PWR/GND), but existing 40-pin packs should still be sufficient.</t>
+  </si>
+  <si>
+    <t>Chassis</t>
+  </si>
+  <si>
+    <t>Line Follower Chassis (3D Printed)</t>
+  </si>
+  <si>
+    <t>Modified 3D Printed Chassis</t>
+  </si>
+  <si>
+    <t>Requires redesign/reprinting of the chassis front extension to mount the wider array and wing sensors.</t>
+  </si>
+  <si>
+    <t>Power Regulator</t>
+  </si>
+  <si>
+    <t>Mini MP1584 DC-DC 3A</t>
+  </si>
+  <si>
+    <t>Increased current draw from 10 LEDs, but the 3A buck converter can easily handle it.</t>
   </si>
   <si>
     <t>Hardware Architecture &amp; Component Sourcing</t>
@@ -49,7 +116,10 @@
     </r>
   </si>
   <si>
-    <t>For contigency, i took 25% of original total</t>
+    <t>Shipping : 200 for polulu ir sensor, 75 for probots, 125 for buffer</t>
+  </si>
+  <si>
+    <t>For contigency, i took 10% of original total</t>
   </si>
   <si>
     <t>Line Total</t>
@@ -91,10 +161,7 @@
     <t>Alternative</t>
   </si>
   <si>
-    <t>Microcontroller</t>
-  </si>
-  <si>
-    <t>ESP32-WROOM-32 DevKit V1 (30-pin)</t>
+    <t>ESP32-WROOM-32 38Pin Development Board</t>
   </si>
   <si>
     <t>https://robu.in/product/esp32-38pin-development-board-wifibluetooth-ultra-low-power-consumption-dual-core/</t>
@@ -112,134 +179,131 @@
     <t>IR Arrray</t>
   </si>
   <si>
-    <t xml:space="preserve">5-Channel TCRT5000 IR Line Tracking Sensor Module
+    <t>Pololu QTR-8A Reflectance Sensor Array (Product Code: Pololu #960)</t>
+  </si>
+  <si>
+    <t>https://www.mgsuperlabs.co.in/estore/QTR-8A-Reflectance-Sensor-Array</t>
+  </si>
+  <si>
+    <t>8 IR LED/phototransistor pairs, 9.52 mm pitch, 3.3V–5.0V operating range, 8 analog voltage outputs, 3.09 g ultra-lightweight, breakaway PCB perforation (can split into 6+2).</t>
+  </si>
+  <si>
+    <t>Sub-millimeter analog resolution eliminates glare from 30 mm vinyl tape. Ultra-lightweight (3.09 g) prevents front overhang inertia and skidding at 500 RPM turns. Breakaway design allows optional 6+2 T-layout.</t>
+  </si>
+  <si>
+    <t>Generic 5-Ch TCRT5000 (Bulkier 30 g PCB, coarse 5-point resolution, prone to ambient light saturation).</t>
+  </si>
+  <si>
+    <t>Motors</t>
+  </si>
+  <si>
+    <t>GA12-N20 6V 500RPM Micro DC Reducer Motor Encoder with Wire</t>
+  </si>
+  <si>
+    <t>https://robu.in/product/ga12-n20-6v-500rpm-micro-dc-reducer-motor-encoder-with-wire/</t>
+  </si>
+  <si>
+    <t>6V DC, 500 RPM rated speed, all-metal reduction gearbox, integrated dual-channel incremental quadrature Hall encoder, 3mm D-shaft</t>
+  </si>
+  <si>
+    <t>500 RPM provides high linear speed to minimize actual run time, while quadrature encoder feedback guarantees precise 90° pivot turns without wheel slip</t>
+  </si>
+  <si>
+    <t>N20 6V 100RPM Encoder Motor (High torque but too slow to maximize the time score during the actual run)</t>
+  </si>
+  <si>
+    <t>Motor driver</t>
+  </si>
+  <si>
+    <t>TB6612FNG Dual H-Bridge Motor Driver Module</t>
+  </si>
+  <si>
+    <t>https://robu.in/product/motor-driver-tb6612fng-module-performance-ultra-small-volume-3-pi-matching-performance-ultra-l298n/</t>
+  </si>
+  <si>
+    <t>VM: 4.5V–15V, 1.2A continuous / 3.2A peak, MOSFET H-Bridge, 3.3V logic</t>
+  </si>
+  <si>
+    <t>MOSFET design has negligible voltage drop (~0.2V) and runs cool compared to bipolar drivers.</t>
+  </si>
+  <si>
+    <t>L298N Module (Drops 2V as waste heat, excessively bulky)</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>Orange 7.4V (2S) 1500mAh 25C LiPo Battery Pack</t>
+  </si>
+  <si>
+    <t>https://robu.in/product/orange-1500mah-2s-25c-7-4-v-lithium-polymer-battery-pack-li-po/</t>
+  </si>
+  <si>
+    <t>7.4V nominal (8.4V max), 1500mAh, 25C discharge (37.5A burst), XT60</t>
+  </si>
+  <si>
+    <t>Provides stiff voltage without sagging under sudden motor stall/acceleration; 2 packs allow back-to-back testing.</t>
+  </si>
+  <si>
+    <t>9V Alkaline Battery (High internal resistance, collapses under motor draw)</t>
+  </si>
+  <si>
+    <t>Battery Charger</t>
+  </si>
+  <si>
+    <t>IMAX B3 AC Pro Compact Balance Charger for 2S-3S LiPo</t>
+  </si>
+  <si>
+    <t>https://robu.in/product/b3ac-compact-balance-charger-2s-3s-lipo/</t>
+  </si>
+  <si>
+    <t>AC 100–240V input, 3 x 800mA dedicated balance charging per cell</t>
+  </si>
+  <si>
+    <t>Essential balancer to prevent cell overcharge and protect battery cycle life.</t>
+  </si>
+  <si>
+    <t>Standard DC 9V Adapter (Dangerous for LiPo, causes puffing/fire)</t>
+  </si>
+  <si>
+    <t>Voltage Regulator</t>
+  </si>
+  <si>
+    <t>SmartElex Mini MP1584 DC-DC 3A Adjustable Buck Module</t>
+  </si>
+  <si>
+    <t>https://robu.in/product/mini-mp1584-dc-dc-adjustable-buck-module-3a/</t>
+  </si>
+  <si>
+    <t>Input: 4.5V–28V, Output: Regulated 5.0V, 3A peak, 96% efficiency</t>
+  </si>
+  <si>
+    <t>Highly efficient step-down from 7.4V LiPo to clean 5V for ESP32 and sensor logic.</t>
+  </si>
+  <si>
+    <t>LM2596 Module (Much larger footprint and unnecessary chassis weight)</t>
+  </si>
+  <si>
+    <t>Line Follower Chassis Compatible with N20 Motor with Clamp (3D Printed, ABS/PETG)</t>
+  </si>
+  <si>
+    <t>https://www.indianhobbycenter.com/products/line-follower-chassis-3d-printed</t>
+  </si>
+  <si>
+    <t>Dimensions: 130 × 129.4 × 3 mm, material: ABS/PETG, includes 2x custom N20 motor mounting clamps, front sensor extension plate</t>
+  </si>
+  <si>
+    <t>Ultra-lightweight and rigid structure dedicated for N20 motors; fits within the 220 X 220 X 220 mm size limit and includes direct clamp hardware.</t>
+  </si>
+  <si>
+    <t>2WD Acrylic Round Chassis Kit (Heavier, generic circular profile without dedicated N20 clamps)</t>
+  </si>
+  <si>
+    <t>Drive Wheels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicone Tire Wheel for N20 Micro Metal Gear Motors
 </t>
-  </si>
-  <si>
-    <t>https://robu.in/product/tcrt5000l-5-channel-tracking-sensor-tracking-module-infrared-sensor/</t>
-  </si>
-  <si>
-    <t>5-ch TCRT5000 array, analog &amp; digital outputs, LM393 comparators, trimmers</t>
-  </si>
-  <si>
-    <t>Analog outputs allow software threshold calibration against glossy vinyl surface reflections.</t>
-  </si>
-  <si>
-    <t>3-Channel IR Array (Fewer sensors, unreliable 90° turn sensing)</t>
-  </si>
-  <si>
-    <t>Motors</t>
-  </si>
-  <si>
-    <t>GA12-N20 6V 500RPM Micro DC Reducer Motor Encoder with Wire</t>
-  </si>
-  <si>
-    <t>https://robu.in/product/ga12-n20-6v-500rpm-micro-dc-reducer-motor-encoder-with-wire/</t>
-  </si>
-  <si>
-    <t>6V DC, 500 RPM rated speed, all-metal reduction gearbox, integrated dual-channel incremental quadrature Hall encoder, 3mm D-shaft</t>
-  </si>
-  <si>
-    <t>500 RPM provides high linear speed to minimize actual run time, while quadrature encoder feedback guarantees precise 90° pivot turns without wheel slip</t>
-  </si>
-  <si>
-    <t>N20 6V 100RPM Encoder Motor (High torque but too slow to maximize the time score during the actual run)</t>
-  </si>
-  <si>
-    <t>Motor driver</t>
-  </si>
-  <si>
-    <t>TB6612FNG Dual H-Bridge Motor Driver Module</t>
-  </si>
-  <si>
-    <t>https://robu.in/product/motor-driver-tb6612fng-module-performance-ultra-small-volume-3-pi-matching-performance-ultra-l298n/</t>
-  </si>
-  <si>
-    <t>VM: 4.5V–15V, 1.2A continuous / 3.2A peak, MOSFET H-Bridge, 3.3V logic</t>
-  </si>
-  <si>
-    <t>MOSFET design has negligible voltage drop (~0.2V) and runs cool compared to bipolar drivers.</t>
-  </si>
-  <si>
-    <t>L298N Module (Drops 2V as waste heat, excessively bulky)</t>
-  </si>
-  <si>
-    <t>Battery</t>
-  </si>
-  <si>
-    <t>Orange 7.4V (2S) 1500mAh 25C LiPo Battery Pack</t>
-  </si>
-  <si>
-    <t>https://robu.in/product/orange-1500mah-2s-25c-7-4-v-lithium-polymer-battery-pack-li-po/</t>
-  </si>
-  <si>
-    <t>7.4V nominal (8.4V max), 1500mAh, 25C discharge (37.5A burst), XT60</t>
-  </si>
-  <si>
-    <t>Provides stiff voltage without sagging under sudden motor stall/acceleration; 2 packs allow back-to-back testing.</t>
-  </si>
-  <si>
-    <t>9V Alkaline Battery (High internal resistance, collapses under motor draw)</t>
-  </si>
-  <si>
-    <t>Battery Charger</t>
-  </si>
-  <si>
-    <t>IMAX B3 AC Pro Compact Balance Charger for 2S-3S LiPo</t>
-  </si>
-  <si>
-    <t>https://robu.in/product/b3ac-compact-balance-charger-2s-3s-lipo/</t>
-  </si>
-  <si>
-    <t>AC 100–240V input, 3 x 800mA dedicated balance charging per cell</t>
-  </si>
-  <si>
-    <t>Essential balancer to prevent cell overcharge and protect battery cycle life.</t>
-  </si>
-  <si>
-    <t>Standard DC 9V Adapter (Dangerous for LiPo, causes puffing/fire)</t>
-  </si>
-  <si>
-    <t>Voltage Regulator</t>
-  </si>
-  <si>
-    <t>SmartElex Mini MP1584 DC-DC 3A Adjustable Buck Module</t>
-  </si>
-  <si>
-    <t>https://robu.in/product/mini-mp1584-dc-dc-adjustable-buck-module-3a/</t>
-  </si>
-  <si>
-    <t>Input: 4.5V–28V, Output: Regulated 5.0V, 3A peak, 96% efficiency</t>
-  </si>
-  <si>
-    <t>Highly efficient step-down from 7.4V LiPo to clean 5V for ESP32 and sensor logic.</t>
-  </si>
-  <si>
-    <t>LM2596 Module (Much larger footprint and unnecessary chassis weight)</t>
-  </si>
-  <si>
-    <t>Chassis</t>
-  </si>
-  <si>
-    <t>Line Follower Chassis Compatible with N20 Motor with Clamp (3D Printed, ABS/PETG)</t>
-  </si>
-  <si>
-    <t>https://www.indianhobbycenter.com/products/line-follower-chassis-3d-printed</t>
-  </si>
-  <si>
-    <t>Dimensions: 130 × 129.4 × 3 mm, material: ABS/PETG, includes 2x custom N20 motor mounting clamps, front sensor extension plate</t>
-  </si>
-  <si>
-    <t>Ultra-lightweight and rigid structure dedicated for N20 motors; fits within the 220 X 220 X 220 mm size limit and includes direct clamp hardware.</t>
-  </si>
-  <si>
-    <t>2WD Acrylic Round Chassis Kit (Heavier, generic circular profile without dedicated N20 clamps)</t>
-  </si>
-  <si>
-    <t>Drive Wheels</t>
-  </si>
-  <si>
-    <t>5908 Series Silicone Tire Wheel for N20 Motors (Pair)</t>
   </si>
   <si>
     <t>https://probots.co.in/silicone-tire-wheel-for-n20-motor.html</t>
@@ -391,7 +455,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -400,9 +464,20 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="16.0"/>
       <color rgb="FF1E3989"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -593,167 +668,169 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="2" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="2" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="2" fontId="11" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="11" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="5" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="5" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="5" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="6" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="6" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="6" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="2" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="2" fillId="6" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf borderId="2" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="5" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="21" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="5" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="6" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="6" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="23" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="21" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="5" fontId="23" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -765,6 +842,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -986,630 +1067,632 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="A2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="14">
+      <c r="A5" s="9"/>
+      <c r="B5" s="16">
         <f>SUM(E8:E23)</f>
-        <v>6597.1</v>
-      </c>
-      <c r="C5" s="15">
-        <v>200.0</v>
-      </c>
-      <c r="D5" s="14">
-        <f>ROUND(B5*0.25, 2)</f>
-        <v>1649.28</v>
-      </c>
-      <c r="E5" s="14">
+        <v>8056.1</v>
+      </c>
+      <c r="C5" s="17">
+        <v>400.0</v>
+      </c>
+      <c r="D5" s="16">
+        <f>ROUND(B5*0.1, 2)</f>
+        <v>805.61</v>
+      </c>
+      <c r="E5" s="16">
         <f>B5+C5+D5</f>
-        <v>8446.38</v>
-      </c>
-      <c r="F5" s="16">
+        <v>9261.71</v>
+      </c>
+      <c r="F5" s="18">
         <f>SUM(C8:C23)</f>
         <v>32</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="9"/>
     </row>
     <row r="6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="B8" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="26">
         <v>2.0</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="27">
         <v>449.0</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="28">
         <f t="shared" ref="E8:E23" si="1">IF(OR(ISBLANK(C8),ISBLANK(D8)),"",C8*D8)</f>
         <v>898</v>
       </c>
-      <c r="F8" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>22</v>
+      <c r="F8" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="32">
+      <c r="A9" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="34">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="35">
+        <v>1849.0</v>
+      </c>
+      <c r="E9" s="36">
+        <f t="shared" si="1"/>
+        <v>1849</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="26">
         <v>2.0</v>
       </c>
-      <c r="D9" s="33">
-        <v>209.0</v>
-      </c>
-      <c r="E9" s="34">
-        <f t="shared" si="1"/>
-        <v>418</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="24">
-        <v>2.0</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="D10" s="27">
         <v>619.0</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="28">
         <f t="shared" si="1"/>
         <v>1238</v>
       </c>
-      <c r="F10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>34</v>
+      <c r="F10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="32">
+      <c r="A11" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="34">
         <v>2.0</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="35">
         <v>149.0</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="36">
         <f t="shared" si="1"/>
         <v>298</v>
       </c>
-      <c r="F11" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>40</v>
+      <c r="F11" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="24">
+      <c r="A12" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="26">
         <v>2.0</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="27">
         <v>1239.0</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="28">
         <f t="shared" si="1"/>
         <v>2478</v>
       </c>
-      <c r="F12" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>46</v>
+      <c r="F12" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="A13" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="34">
         <v>1.0</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="35">
         <v>349.0</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="36">
         <f t="shared" si="1"/>
         <v>349</v>
       </c>
-      <c r="F13" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>52</v>
+      <c r="F13" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="24">
+      <c r="A14" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="26">
         <v>2.0</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="27">
         <v>105.0</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="28">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="F14" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>58</v>
+      <c r="F14" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="32">
+      <c r="A15" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="34">
         <v>1.0</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="35">
         <v>169.0</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="36">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
-      <c r="F15" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>64</v>
+      <c r="F15" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="24">
+      <c r="A16" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="26">
         <v>2.0</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="27">
         <v>169.0</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="28">
         <f t="shared" si="1"/>
         <v>338</v>
       </c>
-      <c r="F16" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>70</v>
+      <c r="F16" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="30" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="32">
+      <c r="A17" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="34">
         <v>1.0</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="35">
         <v>39.0</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="36">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="F17" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>76</v>
+      <c r="F17" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="24">
+      <c r="A18" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="26">
         <v>1.0</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="27">
         <v>13.0</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="28">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F18" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>82</v>
+      <c r="F18" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="19" ht="24.0" customHeight="1">
-      <c r="A19" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="32">
+      <c r="A19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="34">
         <v>1.0</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="35">
         <v>18.0</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="36">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F19" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="43" t="s">
-        <v>88</v>
+      <c r="F19" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="45" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="20" ht="24.0" customHeight="1">
-      <c r="A20" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="25">
+      <c r="A20" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="D20" s="27">
         <v>28.0</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="28">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="I20" s="39" t="s">
-        <v>94</v>
+        <v>56</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="21" ht="24.0" customHeight="1">
-      <c r="A21" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="32">
+      <c r="A21" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="34">
         <v>10.0</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="35">
         <v>0.51</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="36">
         <f t="shared" si="1"/>
         <v>5.1</v>
       </c>
-      <c r="F21" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="H21" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="I21" s="43" t="s">
-        <v>100</v>
+      <c r="F21" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="45" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="22" ht="24.0" customHeight="1">
-      <c r="A22" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="24">
+      <c r="A22" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="26">
         <v>1.0</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="27">
         <v>49.0</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="28">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="F22" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="I22" s="47" t="s">
-        <v>106</v>
+      <c r="F22" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="23" ht="24.0" customHeight="1">
-      <c r="A23" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="32">
+      <c r="A23" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="34">
         <v>1.0</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="35">
         <v>49.0</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="36">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="F23" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>112</v>
+      <c r="F23" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="24" ht="24.0" customHeight="1">
-      <c r="A24" s="50" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="52">
+      <c r="A24" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="53"/>
+      <c r="C24" s="54">
         <f>SUM(C8:C23)</f>
         <v>32</v>
       </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="53">
+      <c r="D24" s="53"/>
+      <c r="E24" s="55">
         <f>SUM(E8:E23)</f>
-        <v>6597.1</v>
-      </c>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
+        <v>8056.1</v>
+      </c>
+      <c r="F24" s="56"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1636,4 +1719,106 @@
   <pageSetup paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId18"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="12.88"/>
+    <col customWidth="1" min="2" max="2" width="25.75"/>
+    <col customWidth="1" min="3" max="3" width="28.63"/>
+    <col customWidth="1" min="4" max="4" width="81.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>